--- a/generated_pivot.xlsx
+++ b/generated_pivot.xlsx
@@ -9,6 +9,47 @@
     <pivotCache cacheId="5" r:id="rId3"/>
   </pivotCaches>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+</styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -33,34 +74,16 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Year" numFmtId="0">
-      <sharedItems count="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2025" maxValue="2026" count="2">
         <n v="2025"/>
         <n v="2026"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Revenue" numFmtId="0">
-      <sharedItems count="8">
-        <n v="10000"/>
-        <n v="5000"/>
-        <n v="7000"/>
-        <n v="8000"/>
-        <n v="6000"/>
-        <n v="9000"/>
-        <n v="4000"/>
-        <n v="11000"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4000" maxValue="11000"/>
     </cacheField>
     <cacheField name="Quantity" numFmtId="0">
-      <sharedItems count="8">
-        <n v="10"/>
-        <n v="5"/>
-        <n v="7"/>
-        <n v="8"/>
-        <n v="6"/>
-        <n v="9"/>
-        <n v="4"/>
-        <n v="11"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="11"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
@@ -142,7 +165,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="5" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" createdVersion="8" useAutoFormatting="1" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="5">
     <pivotField showAll="0" axis="axisRow">
@@ -177,16 +200,16 @@
   </rowFields>
   <rowItems count="5">
     <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="0"/>
+      <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -197,7 +220,7 @@
   </colFields>
   <colItems count="4">
     <i>
-      <x v="0"/>
+      <x/>
     </i>
     <i>
       <x v="1"/>
@@ -482,7 +505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
